--- a/input/mapping/011. OCB_GOLD_TCKH_V_HT_CP_UPL_PHAT.xlsx
+++ b/input/mapping/011. OCB_GOLD_TCKH_V_HT_CP_UPL_PHAT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/PhatNT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="384" documentId="8_{99BA2690-504E-4BB4-8589-AE4ABC69581E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80B41C4A-7765-49F8-B75E-0519925E6257}"/>
+  <xr:revisionPtr revIDLastSave="385" documentId="8_{99BA2690-504E-4BB4-8589-AE4ABC69581E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{189A8B5E-CC4B-4473-B09C-038852588DC6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="838" activeTab="1" xr2:uid="{CDFBD334-D065-4A45-A0C3-FE4463186C1A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="838" firstSheet="1" xr2:uid="{CDFBD334-D065-4A45-A0C3-FE4463186C1A}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -897,6 +897,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -929,21 +944,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1356,60 +1356,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="45" customHeight="1">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="60"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="65"/>
       <c r="N1" s="25"/>
       <c r="O1" s="25"/>
     </row>
     <row r="2" spans="1:21" ht="19.899999999999999" customHeight="1">
-      <c r="B2" s="64" t="s">
+      <c r="B2" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="64"/>
+      <c r="C2" s="69"/>
       <c r="D2" s="15"/>
-      <c r="E2" s="64" t="s">
+      <c r="E2" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="64"/>
+      <c r="F2" s="69"/>
       <c r="G2" s="15"/>
-      <c r="H2" s="63" t="s">
+      <c r="H2" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="63"/>
+      <c r="I2" s="68"/>
       <c r="L2" s="27"/>
     </row>
     <row r="3" spans="1:21" ht="36.75" customHeight="1">
-      <c r="B3" s="68" t="s">
+      <c r="B3" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="67" t="s">
+      <c r="C3" s="73"/>
+      <c r="D3" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="66" t="s">
+      <c r="E3" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="66"/>
-      <c r="G3" s="67" t="s">
+      <c r="F3" s="71"/>
+      <c r="G3" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="65" t="s">
+      <c r="H3" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="65"/>
+      <c r="I3" s="70"/>
       <c r="J3" s="28"/>
       <c r="L3" s="28"/>
       <c r="M3" s="28"/>
@@ -1419,14 +1419,14 @@
       <c r="U3" s="30"/>
     </row>
     <row r="4" spans="1:21" ht="37.5" customHeight="1">
-      <c r="B4" s="68"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="70"/>
       <c r="J4" s="28"/>
       <c r="L4" s="28"/>
       <c r="M4" s="28"/>
@@ -1446,7 +1446,7 @@
       <c r="L5" s="35"/>
       <c r="M5" s="36"/>
       <c r="N5" s="36"/>
-      <c r="O5" s="61"/>
+      <c r="O5" s="66"/>
     </row>
     <row r="6" spans="1:21" ht="19.899999999999999" customHeight="1">
       <c r="B6" s="31"/>
@@ -1460,7 +1460,7 @@
       <c r="L6" s="35"/>
       <c r="M6" s="37"/>
       <c r="N6" s="37"/>
-      <c r="O6" s="61"/>
+      <c r="O6" s="66"/>
     </row>
     <row r="7" spans="1:21" ht="19.899999999999999" customHeight="1">
       <c r="B7" s="31"/>
@@ -1496,7 +1496,7 @@
       <c r="I8" s="42"/>
       <c r="J8" s="37"/>
       <c r="K8" s="43"/>
-      <c r="L8" s="62"/>
+      <c r="L8" s="67"/>
       <c r="M8" s="30"/>
       <c r="N8" s="41"/>
       <c r="O8" s="30"/>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="I9" s="42"/>
       <c r="J9" s="37"/>
-      <c r="L9" s="62"/>
+      <c r="L9" s="67"/>
       <c r="M9" s="30"/>
       <c r="N9" s="41"/>
       <c r="O9" s="30"/>
@@ -1650,176 +1650,151 @@
       <c r="J21" s="30"/>
     </row>
     <row r="33" spans="2:15" ht="19.899999999999999" customHeight="1">
-      <c r="B33" s="71"/>
-      <c r="C33" s="71"/>
-      <c r="D33" s="71"/>
-      <c r="E33" s="71"/>
-      <c r="F33" s="71"/>
-      <c r="G33" s="71"/>
-      <c r="H33" s="71"/>
-      <c r="I33" s="71"/>
-      <c r="J33" s="71"/>
-      <c r="K33" s="71"/>
-      <c r="L33" s="71"/>
-      <c r="M33" s="71"/>
-      <c r="N33" s="71"/>
-      <c r="O33" s="71"/>
+      <c r="B33" s="61"/>
+      <c r="C33" s="61"/>
+      <c r="D33" s="61"/>
+      <c r="E33" s="61"/>
+      <c r="F33" s="61"/>
+      <c r="G33" s="61"/>
+      <c r="H33" s="61"/>
+      <c r="I33" s="61"/>
+      <c r="J33" s="61"/>
+      <c r="K33" s="61"/>
+      <c r="L33" s="61"/>
+      <c r="M33" s="61"/>
+      <c r="N33" s="61"/>
+      <c r="O33" s="61"/>
     </row>
     <row r="34" spans="2:15" ht="19.899999999999999" customHeight="1">
-      <c r="B34" s="71"/>
-      <c r="C34" s="71"/>
-      <c r="D34" s="71"/>
-      <c r="E34" s="73"/>
-      <c r="F34" s="71"/>
-      <c r="G34" s="73"/>
-      <c r="H34" s="71"/>
-      <c r="I34" s="71"/>
-      <c r="J34" s="71"/>
-      <c r="K34" s="71"/>
-      <c r="L34" s="71"/>
-      <c r="M34" s="71"/>
-      <c r="N34" s="71"/>
-      <c r="O34" s="71"/>
+      <c r="B34" s="61"/>
+      <c r="C34" s="61"/>
+      <c r="D34" s="61"/>
+      <c r="E34" s="62"/>
+      <c r="F34" s="61"/>
+      <c r="G34" s="62"/>
+      <c r="H34" s="61"/>
+      <c r="I34" s="61"/>
+      <c r="J34" s="61"/>
+      <c r="K34" s="61"/>
+      <c r="L34" s="61"/>
+      <c r="M34" s="61"/>
+      <c r="N34" s="61"/>
+      <c r="O34" s="61"/>
     </row>
     <row r="35" spans="2:15" ht="19.899999999999999" customHeight="1">
-      <c r="B35" s="69"/>
-      <c r="C35" s="69"/>
-      <c r="D35" s="69"/>
-      <c r="E35" s="70"/>
-      <c r="F35" s="71"/>
-      <c r="G35" s="72"/>
-      <c r="H35" s="69"/>
-      <c r="I35" s="69"/>
-      <c r="J35" s="69"/>
-      <c r="K35" s="69"/>
-      <c r="L35" s="69"/>
-      <c r="M35" s="69"/>
-      <c r="N35" s="69"/>
-      <c r="O35" s="69"/>
+      <c r="B35" s="60"/>
+      <c r="C35" s="60"/>
+      <c r="D35" s="60"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="61"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="60"/>
+      <c r="I35" s="60"/>
+      <c r="J35" s="60"/>
+      <c r="K35" s="60"/>
+      <c r="L35" s="60"/>
+      <c r="M35" s="60"/>
+      <c r="N35" s="60"/>
+      <c r="O35" s="60"/>
     </row>
     <row r="36" spans="2:15" ht="19.899999999999999" customHeight="1">
-      <c r="B36" s="69"/>
-      <c r="C36" s="69"/>
-      <c r="D36" s="69"/>
-      <c r="E36" s="70"/>
-      <c r="F36" s="71"/>
-      <c r="G36" s="72"/>
-      <c r="H36" s="69"/>
-      <c r="I36" s="69"/>
-      <c r="J36" s="69"/>
-      <c r="K36" s="69"/>
-      <c r="L36" s="69"/>
-      <c r="M36" s="69"/>
-      <c r="N36" s="69"/>
-      <c r="O36" s="69"/>
+      <c r="B36" s="60"/>
+      <c r="C36" s="60"/>
+      <c r="D36" s="60"/>
+      <c r="E36" s="59"/>
+      <c r="F36" s="61"/>
+      <c r="G36" s="58"/>
+      <c r="H36" s="60"/>
+      <c r="I36" s="60"/>
+      <c r="J36" s="60"/>
+      <c r="K36" s="60"/>
+      <c r="L36" s="60"/>
+      <c r="M36" s="60"/>
+      <c r="N36" s="60"/>
+      <c r="O36" s="60"/>
     </row>
     <row r="37" spans="2:15" ht="19.899999999999999" customHeight="1">
-      <c r="B37" s="69"/>
-      <c r="C37" s="69"/>
-      <c r="D37" s="69"/>
-      <c r="E37" s="70"/>
-      <c r="F37" s="71"/>
-      <c r="G37" s="72"/>
-      <c r="H37" s="69"/>
-      <c r="I37" s="69"/>
-      <c r="J37" s="69"/>
-      <c r="K37" s="69"/>
-      <c r="L37" s="69"/>
-      <c r="M37" s="69"/>
-      <c r="N37" s="69"/>
-      <c r="O37" s="69"/>
+      <c r="B37" s="60"/>
+      <c r="C37" s="60"/>
+      <c r="D37" s="60"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="61"/>
+      <c r="G37" s="58"/>
+      <c r="H37" s="60"/>
+      <c r="I37" s="60"/>
+      <c r="J37" s="60"/>
+      <c r="K37" s="60"/>
+      <c r="L37" s="60"/>
+      <c r="M37" s="60"/>
+      <c r="N37" s="60"/>
+      <c r="O37" s="60"/>
     </row>
     <row r="38" spans="2:15" ht="19.899999999999999" customHeight="1">
-      <c r="B38" s="72"/>
-      <c r="C38" s="72"/>
-      <c r="D38" s="72"/>
-      <c r="E38" s="70"/>
-      <c r="F38" s="70"/>
-      <c r="G38" s="72"/>
-      <c r="H38" s="72"/>
-      <c r="I38" s="72"/>
-      <c r="J38" s="72"/>
-      <c r="K38" s="72"/>
-      <c r="L38" s="72"/>
-      <c r="M38" s="72"/>
-      <c r="N38" s="72"/>
-      <c r="O38" s="72"/>
+      <c r="B38" s="58"/>
+      <c r="C38" s="58"/>
+      <c r="D38" s="58"/>
+      <c r="E38" s="59"/>
+      <c r="F38" s="59"/>
+      <c r="G38" s="58"/>
+      <c r="H38" s="58"/>
+      <c r="I38" s="58"/>
+      <c r="J38" s="58"/>
+      <c r="K38" s="58"/>
+      <c r="L38" s="58"/>
+      <c r="M38" s="58"/>
+      <c r="N38" s="58"/>
+      <c r="O38" s="58"/>
     </row>
     <row r="39" spans="2:15" ht="19.899999999999999" customHeight="1">
-      <c r="B39" s="72"/>
-      <c r="C39" s="72"/>
-      <c r="D39" s="72"/>
-      <c r="E39" s="70"/>
-      <c r="F39" s="70"/>
-      <c r="G39" s="72"/>
-      <c r="H39" s="72"/>
-      <c r="I39" s="72"/>
-      <c r="J39" s="72"/>
-      <c r="K39" s="72"/>
-      <c r="L39" s="72"/>
-      <c r="M39" s="72"/>
-      <c r="N39" s="72"/>
-      <c r="O39" s="72"/>
+      <c r="B39" s="58"/>
+      <c r="C39" s="58"/>
+      <c r="D39" s="58"/>
+      <c r="E39" s="59"/>
+      <c r="F39" s="59"/>
+      <c r="G39" s="58"/>
+      <c r="H39" s="58"/>
+      <c r="I39" s="58"/>
+      <c r="J39" s="58"/>
+      <c r="K39" s="58"/>
+      <c r="L39" s="58"/>
+      <c r="M39" s="58"/>
+      <c r="N39" s="58"/>
+      <c r="O39" s="58"/>
     </row>
     <row r="40" spans="2:15" ht="19.899999999999999" customHeight="1">
-      <c r="B40" s="72"/>
-      <c r="C40" s="72"/>
-      <c r="D40" s="72"/>
-      <c r="E40" s="70"/>
-      <c r="F40" s="70"/>
-      <c r="G40" s="72"/>
-      <c r="H40" s="72"/>
-      <c r="I40" s="72"/>
-      <c r="J40" s="72"/>
-      <c r="K40" s="72"/>
-      <c r="L40" s="72"/>
-      <c r="M40" s="72"/>
-      <c r="N40" s="72"/>
-      <c r="O40" s="72"/>
+      <c r="B40" s="58"/>
+      <c r="C40" s="58"/>
+      <c r="D40" s="58"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="58"/>
+      <c r="H40" s="58"/>
+      <c r="I40" s="58"/>
+      <c r="J40" s="58"/>
+      <c r="K40" s="58"/>
+      <c r="L40" s="58"/>
+      <c r="M40" s="58"/>
+      <c r="N40" s="58"/>
+      <c r="O40" s="58"/>
     </row>
     <row r="41" spans="2:15" ht="19.899999999999999" customHeight="1">
-      <c r="B41" s="72"/>
-      <c r="C41" s="72"/>
-      <c r="D41" s="72"/>
-      <c r="E41" s="70"/>
-      <c r="F41" s="70"/>
-      <c r="G41" s="72"/>
-      <c r="H41" s="72"/>
-      <c r="I41" s="72"/>
-      <c r="J41" s="72"/>
-      <c r="K41" s="72"/>
-      <c r="L41" s="72"/>
-      <c r="M41" s="72"/>
-      <c r="N41" s="72"/>
-      <c r="O41" s="72"/>
+      <c r="B41" s="58"/>
+      <c r="C41" s="58"/>
+      <c r="D41" s="58"/>
+      <c r="E41" s="59"/>
+      <c r="F41" s="59"/>
+      <c r="G41" s="58"/>
+      <c r="H41" s="58"/>
+      <c r="I41" s="58"/>
+      <c r="J41" s="58"/>
+      <c r="K41" s="58"/>
+      <c r="L41" s="58"/>
+      <c r="M41" s="58"/>
+      <c r="N41" s="58"/>
+      <c r="O41" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="G40:O40"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="G41:O41"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="G38:O38"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="G39:O39"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="G36:O36"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="G37:O37"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="G35:O35"/>
-    <mergeCell ref="B33:O33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="G34:O34"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="O5:O6"/>
     <mergeCell ref="L8:L9"/>
@@ -1831,6 +1806,31 @@
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="B3:C4"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="G35:O35"/>
+    <mergeCell ref="B33:O33"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="G34:O34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="G36:O36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="G37:O37"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="G38:O38"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="G39:O39"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="G40:O40"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="G41:O41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1876,7 +1876,7 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="57" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2425,6 +2425,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -2596,27 +2615,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F3B0E1D-FFBD-402C-8973-C7BEB76FCD06}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BD988DF-592B-4F88-8221-BDE140EDD1EA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2624,5 +2624,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BD988DF-592B-4F88-8221-BDE140EDD1EA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F3B0E1D-FFBD-402C-8973-C7BEB76FCD06}"/>
 </file>